--- a/data/excelphase3.1.xlsx
+++ b/data/excelphase3.1.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Documents\Excelium\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C548E0-2284-45EE-969E-EDAC36F1DAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6D2148-AFAD-4C7C-93CF-E8AAF8CFFF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2273" yWindow="1373" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="feuille1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/data/excelphase3.1.xlsx
+++ b/data/excelphase3.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Documents\Excelium\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6D2148-AFAD-4C7C-93CF-E8AAF8CFFF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2896623-38FC-4F47-84BF-404ABB6FA076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2273" yWindow="1373" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2948" yWindow="2048" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feuille1" sheetId="1" r:id="rId1"/>
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -431,6 +431,18 @@
         <v>30</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>50</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <f>A5+B5</f>
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
